--- a/NowNew/엑셀데이터표.xlsx
+++ b/NowNew/엑셀데이터표.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Pi2Work\NowNew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE69D3D6-3BD8-4B54-95EF-B9263FDC9BAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE784294-4790-46F9-ADBB-E8F92A0B3849}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{27E991D5-0F2F-4CF4-8F14-595658F36E2E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>단가</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,11 +39,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>가상분석&gt;데이터표&gt;행=''&gt;열='h7'</t>
+    <t>가상분석&gt;데이터표&gt;행='c2'&gt;열='c3'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>가상분석&gt;데이터표&gt;행='c2'&gt;열='c3'</t>
+    <t>가상분석&gt;데이터표&gt;열='i2'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -449,8 +449,12 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="H2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
@@ -463,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -479,10 +483,10 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
         <v>4</v>
-      </c>
-      <c r="H6" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -499,12 +503,10 @@
       <c r="E7" s="1">
         <v>3500</v>
       </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
+      <c r="H7" s="1"/>
       <c r="I7" s="3">
-        <f>H7*I3</f>
-        <v>1000</v>
+        <f>I2*I3</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -522,11 +524,11 @@
         <v>3500</v>
       </c>
       <c r="H8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1">
-        <f t="dataTable" ref="I8:I12" dt2D="0" dtr="0" r1="H7"/>
-        <v>2000</v>
+        <f t="dataTable" ref="I8:I12" dt2D="0" dtr="0" r1="I2"/>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -543,10 +545,10 @@
         <v>7000</v>
       </c>
       <c r="H9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -563,10 +565,10 @@
         <v>10500</v>
       </c>
       <c r="H10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="1">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -583,10 +585,10 @@
         <v>14000</v>
       </c>
       <c r="H11" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" s="1">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -603,14 +605,15 @@
         <v>17500</v>
       </c>
       <c r="H12" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" s="1">
-        <v>6000</v>
+        <v>2500</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>